--- a/AERA_1.2_WD_Threat_Control_Test_Matrix.xlsx
+++ b/AERA_1.2_WD_Threat_Control_Test_Matrix.xlsx
@@ -1,11 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Threats" sheetId="1" r:id="R0cbaa08e63cb47fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="2" r:id="Rda35c87859924752"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="Threats" sheetId="1" r:id="R5bdb58d2c93245b4"/>
+    <sheet name="Control" sheetId="2" r:id="R4174285e89d24440"/>
+  </sheets>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1351,7 +1352,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cf364cff76a4c3b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29a936d0560f4d57"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1419,25 +1420,25 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="99" t="str">
-        <x:v>Controlled date</x:v>
+        <x:v>Build ID</x:v>
       </x:c>
       <x:c r="B6" s="100" t="str">
-        <x:v>2026-08-07</x:v>
+        <x:v>AERA-001-1.2WD-20260807.1</x:v>
       </x:c>
       <x:c r="D6" t="str">
         <x:v>Rows using AERA-THR gap controls</x:v>
       </x:c>
       <x:c r="E6" t="n">
-        <x:f>COUNTIF('Threats'!C2:C26,"*AERA-THR-*")</x:f>
-        <x:v>0</x:v>
+        <x:f>IF(ISNUMBER(SEARCH("AERA-THR-",'Threats'!C11)),1,0)+IF(ISNUMBER(SEARCH("AERA-THR-",'Threats'!C17)),1,0)+IF(ISNUMBER(SEARCH("AERA-THR-",'Threats'!C21)),1,0)+IF(ISNUMBER(SEARCH("AERA-THR-",'Threats'!C22)),1,0)+IF(ISNUMBER(SEARCH("AERA-THR-",'Threats'!C23)),1,0)+IF(ISNUMBER(SEARCH("AERA-THR-",'Threats'!C26)),1,0)</x:f>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="99" t="str">
-        <x:v>Author / owner</x:v>
+        <x:v>Controlled date</x:v>
       </x:c>
       <x:c r="B7" s="100" t="str">
-        <x:v>Angelis Pseftis / independent author</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
       <x:c r="D7" t="str">
         <x:v>Rows with required evidence</x:v>
@@ -1449,17 +1450,33 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="99" t="str">
-        <x:v>Status</x:v>
+        <x:v>Author / owner</x:v>
       </x:c>
       <x:c r="B8" s="100" t="str">
-        <x:v>Working Draft; independently authored; no NIST endorsement or support claim</x:v>
+        <x:v>Angelis Pseftis / independent author</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="99" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="B9" s="100" t="str">
+        <x:v>Working Draft; independently authored; no NIST endorsement or support claim</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="99" t="str">
+        <x:v>Public snapshot</x:v>
+      </x:c>
+      <x:c r="B10" s="100" t="str">
+        <x:v>2026-08-08; https://github.com/redxking/AERA; formal public review not open</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="99" t="str">
         <x:v>Source rule</x:v>
       </x:c>
-      <x:c r="B9" s="100" t="str">
+      <x:c r="B11" s="100" t="str">
         <x:v>Generated from the same controlled source used for the master specification</x:v>
       </x:c>
     </x:row>
